--- a/Result/profitability/6206.xlsx
+++ b/Result/profitability/6206.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.17</v>
       </c>
       <c r="M2" t="n">
-        <v>1.76</v>
+        <v>2.02125</v>
       </c>
       <c r="N2" t="n">
-        <v>42.92</v>
+        <v>43.27</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.55</v>
       </c>
       <c r="M3" t="n">
-        <v>1.7875</v>
+        <v>1.9425</v>
       </c>
       <c r="N3" t="n">
-        <v>41.815</v>
+        <v>42.035</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.88</v>
       </c>
       <c r="M4" t="n">
-        <v>1.75</v>
+        <v>1.89375</v>
       </c>
       <c r="N4" t="n">
-        <v>40.72875</v>
+        <v>40.825</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.36</v>
       </c>
       <c r="M5" t="n">
-        <v>1.63625</v>
+        <v>1.87625</v>
       </c>
       <c r="N5" t="n">
-        <v>39.335</v>
+        <v>39.52625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>1.51</v>
       </c>
       <c r="M6" t="n">
-        <v>1.6375</v>
+        <v>1.87</v>
       </c>
       <c r="N6" t="n">
-        <v>38.705</v>
+        <v>39.01750000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.92</v>
       </c>
       <c r="M7" t="n">
-        <v>1.6825</v>
+        <v>1.915</v>
       </c>
       <c r="N7" t="n">
-        <v>38.14250000000001</v>
+        <v>38.16125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>2.13</v>
       </c>
       <c r="M8" t="n">
-        <v>1.75375</v>
+        <v>1.8675</v>
       </c>
       <c r="N8" t="n">
-        <v>37.14</v>
+        <v>37.11</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6206</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1882</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1028</v>
+      </c>
+      <c r="E75" t="n">
+        <v>854</v>
+      </c>
+      <c r="F75" t="n">
+        <v>45.39</v>
+      </c>
+      <c r="G75" t="n">
+        <v>581</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>30.89%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>13</v>
+      </c>
+      <c r="J75" t="n">
+        <v>594</v>
+      </c>
+      <c r="K75" t="n">
+        <v>489</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.04125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>44.23125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.9100000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3625498007968129</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.240000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.005259697567389865</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.530000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.03488372093023262</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
